--- a/TCC/data.xlsx
+++ b/TCC/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Na\3.UEH 6\tc công\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A128A530-D7F6-4E46-B436-EFB8824AB5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE4DD49-216A-4132-958F-7734B917A83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5BF46FC1-623A-4E5F-8204-67DC6C3B88A1}"/>
   </bookViews>
@@ -89,9 +89,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,107 +425,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F88CA7-EBEB-4BB8-A596-868FE942CD80}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>1985</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>0</v>
       </c>
       <c r="D2">
         <v>238.64780531340301</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2">
         <v>4.2060000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>1986</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>0</v>
       </c>
       <c r="D3">
         <v>436.41929677222498</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>3.9550000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>1987</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>0</v>
       </c>
       <c r="D4">
         <v>595.24748870160602</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>3.7170000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>1988</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>0</v>
       </c>
       <c r="D5">
         <v>404.55930507888797</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>3.6230000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>1989</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>0</v>
       </c>
       <c r="D6">
         <v>98.107017215957697</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>3.641</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>1990</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>0</v>
       </c>
       <c r="D7">
@@ -535,15 +531,15 @@
       <c r="E7">
         <v>50.044826109398201</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>3.6019999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>1991</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>0</v>
       </c>
       <c r="D8">
@@ -552,15 +548,15 @@
       <c r="E8">
         <v>50.0021750879596</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8">
         <v>3.524</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>1992</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>0</v>
       </c>
       <c r="D9">
@@ -569,15 +565,15 @@
       <c r="E9">
         <v>49.959203426211602</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9">
         <v>3.3530000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>1993</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="D10">
@@ -586,15 +582,15 @@
       <c r="E10">
         <v>49.915316984609902</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>3.1720000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>1994</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="D11">
@@ -603,15 +599,15 @@
       <c r="E11">
         <v>49.863560162472197</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>2.9409999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>1995</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="D12">
@@ -620,15 +616,15 @@
       <c r="E12">
         <v>49.804748606230802</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12">
         <v>2.7</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>1996</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
         <v>1</v>
       </c>
       <c r="D13">
@@ -637,15 +633,15 @@
       <c r="E13">
         <v>49.748122338353497</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13">
         <v>2.468</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>1997</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14">
         <v>1</v>
       </c>
       <c r="D14">
@@ -654,15 +650,15 @@
       <c r="E14">
         <v>49.610351909074502</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14">
         <v>2.274</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="A15">
         <v>1998</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <v>1</v>
       </c>
       <c r="D15">
@@ -671,15 +667,15 @@
       <c r="E15">
         <v>49.583223164179699</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15">
         <v>2.0979999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>1999</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16">
         <v>1</v>
       </c>
       <c r="D16">
@@ -688,15 +684,15 @@
       <c r="E16">
         <v>49.624620728493099</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16">
         <v>1.9990000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>2000</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
@@ -708,15 +704,15 @@
       <c r="E17">
         <v>49.5167647635447</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17">
         <v>2.028</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>2001</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18">
         <v>1</v>
       </c>
       <c r="C18">
@@ -728,15 +724,15 @@
       <c r="E18">
         <v>49.587640701632203</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18">
         <v>2.0230000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>2002</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19">
         <v>1</v>
       </c>
       <c r="C19">
@@ -748,15 +744,15 @@
       <c r="E19">
         <v>49.490283155425701</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19">
         <v>2.0059999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>2003</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20">
         <v>1</v>
       </c>
       <c r="C20">
@@ -768,15 +764,15 @@
       <c r="E20">
         <v>49.4087911602509</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20">
         <v>1.9990000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>2004</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
@@ -788,15 +784,15 @@
       <c r="E21">
         <v>49.342974336207497</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21">
         <v>1.968</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="A22">
         <v>2005</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22">
         <v>1</v>
       </c>
       <c r="C22">
@@ -808,15 +804,15 @@
       <c r="E22">
         <v>49.400473879245702</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22">
         <v>1.887</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="A23">
         <v>2006</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23">
         <v>1</v>
       </c>
       <c r="C23">
@@ -828,15 +824,15 @@
       <c r="E23">
         <v>49.451795847119698</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23">
         <v>1.873</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="A24">
         <v>2007</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24">
         <v>1</v>
       </c>
       <c r="C24">
@@ -848,15 +844,15 @@
       <c r="E24">
         <v>49.502030294261402</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24">
         <v>1.911</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>2008</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
@@ -868,15 +864,15 @@
       <c r="E25">
         <v>49.475448894455198</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25">
         <v>1.9330000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>2009</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26">
         <v>1</v>
       </c>
       <c r="C26">
@@ -888,15 +884,15 @@
       <c r="E26">
         <v>49.4390523913276</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26">
         <v>1.92</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="A27">
         <v>2010</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
@@ -908,15 +904,15 @@
       <c r="E27">
         <v>49.148092796189097</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27">
         <v>1.9059999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="A28">
         <v>2011</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
@@ -928,15 +924,15 @@
       <c r="E28">
         <v>49.053090756413702</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28">
         <v>1.927</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="A29">
         <v>2012</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
@@ -948,15 +944,15 @@
       <c r="E29">
         <v>49.253776134015197</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29">
         <v>1.9670000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="A30">
         <v>2013</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
@@ -968,15 +964,15 @@
       <c r="E30">
         <v>49.287159037329999</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30">
         <v>1.98</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>2014</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
@@ -988,15 +984,15 @@
       <c r="E31">
         <v>49.339269940774102</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31">
         <v>2.09</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="A32">
         <v>2015</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
@@ -1008,15 +1004,15 @@
       <c r="E32">
         <v>49.122604277303701</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32">
         <v>2.1</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="A33">
         <v>2016</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
@@ -1028,15 +1024,15 @@
       <c r="E33">
         <v>49.103486731382802</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="A34">
         <v>2017</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
@@ -1048,15 +1044,15 @@
       <c r="E34">
         <v>48.824323478967699</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34">
         <v>1.9850000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="A35">
         <v>2018</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
@@ -1068,15 +1064,15 @@
       <c r="E35">
         <v>48.732896476811803</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35">
         <v>1.88</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="A36">
         <v>2019</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
@@ -1088,15 +1084,15 @@
       <c r="E36">
         <v>48.301058486393202</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36">
         <v>1.9430000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="A37">
         <v>2020</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
@@ -1108,15 +1104,15 @@
       <c r="E37">
         <v>48.0971932185412</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37">
         <v>1.9570000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="A38">
         <v>2021</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
@@ -1128,15 +1124,15 @@
       <c r="E38">
         <v>48.529884614099998</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38">
         <v>1.9419999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="A39">
         <v>2022</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39">
         <v>1</v>
       </c>
       <c r="C39">
@@ -1148,15 +1144,15 @@
       <c r="E39">
         <v>48.592130777752899</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39">
         <v>1.927</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="A40">
         <v>2023</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
@@ -1168,19 +1164,9 @@
       <c r="E40">
         <v>48.758884846066699</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40">
         <v>1.913</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D41"/>
-      <c r="E41"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TCC/data.xlsx
+++ b/TCC/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Na\3.UEH 6\tc công\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE4DD49-216A-4132-958F-7734B917A83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AC7893-DF06-4B93-9275-25B01D8B34EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5BF46FC1-623A-4E5F-8204-67DC6C3B88A1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Hexp</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Policy</t>
+  </si>
+  <si>
+    <t>UP</t>
   </si>
 </sst>
 </file>
@@ -89,8 +92,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,10 +429,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F88CA7-EBEB-4BB8-A596-868FE942CD80}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -447,8 +451,11 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1985</v>
       </c>
@@ -461,8 +468,11 @@
       <c r="F2">
         <v>4.2060000000000004</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="1">
+        <v>19.0672575059852</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1986</v>
       </c>
@@ -475,8 +485,11 @@
       <c r="F3">
         <v>3.9550000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="1">
+        <v>19.057454233428299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1987</v>
       </c>
@@ -489,8 +502,11 @@
       <c r="F4">
         <v>3.7170000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="1">
+        <v>19.0506212640251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1988</v>
       </c>
@@ -503,8 +519,11 @@
       <c r="F5">
         <v>3.6230000000000002</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="1">
+        <v>19.046797232134399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1989</v>
       </c>
@@ -517,8 +536,11 @@
       <c r="F6">
         <v>3.641</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="1">
+        <v>19.0530524987416</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1990</v>
       </c>
@@ -534,8 +556,11 @@
       <c r="F7">
         <v>3.6019999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="1">
+        <v>19.173503965162599</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1991</v>
       </c>
@@ -551,8 +576,11 @@
       <c r="F8">
         <v>3.524</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="1">
+        <v>19.4396801924029</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1992</v>
       </c>
@@ -568,8 +596,11 @@
       <c r="F9">
         <v>3.3530000000000002</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="1">
+        <v>19.825251002666501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1993</v>
       </c>
@@ -585,8 +616,11 @@
       <c r="F10">
         <v>3.1720000000000002</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="1">
+        <v>20.305767948795602</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1994</v>
       </c>
@@ -602,8 +636,11 @@
       <c r="F11">
         <v>2.9409999999999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="1">
+        <v>20.856782583632199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1995</v>
       </c>
@@ -619,8 +656,11 @@
       <c r="F12">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="1">
+        <v>21.453846460018301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1996</v>
       </c>
@@ -636,8 +676,11 @@
       <c r="F13">
         <v>2.468</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="1">
+        <v>22.072511130795998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1997</v>
       </c>
@@ -653,8 +696,11 @@
       <c r="F14">
         <v>2.274</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="1">
+        <v>22.688328148807301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1998</v>
       </c>
@@ -670,8 +716,11 @@
       <c r="F15">
         <v>2.0979999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="1">
+        <v>23.2768490668943</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1999</v>
       </c>
@@ -687,16 +736,19 @@
       <c r="F16">
         <v>1.9990000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="1">
+        <v>23.821227889252199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2000</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17">
-        <v>4.1075272600000003</v>
+      <c r="C17" s="1">
+        <v>34.580650329999997</v>
       </c>
       <c r="D17">
         <v>404.029784055118</v>
@@ -707,16 +759,19 @@
       <c r="F17">
         <v>2.028</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="1">
+        <v>24.3672526919772</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2001</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18">
-        <v>4.8010749800000001</v>
+      <c r="C18" s="1">
+        <v>29.701490400000001</v>
       </c>
       <c r="D18">
         <v>419.20567758090101</v>
@@ -727,16 +782,19 @@
       <c r="F18">
         <v>2.0230000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="1">
+        <v>24.948936272514299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2002</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19">
-        <v>3.8707585299999998</v>
+      <c r="C19" s="1">
+        <v>34.542232509999998</v>
       </c>
       <c r="D19">
         <v>445.13286181731303</v>
@@ -747,16 +805,19 @@
       <c r="F19">
         <v>2.0059999999999998</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="1">
+        <v>25.554092566565899</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2003</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20">
-        <v>3.94229889</v>
+      <c r="C20" s="1">
+        <v>34.542835240000002</v>
       </c>
       <c r="D20">
         <v>497.11708924925603</v>
@@ -767,16 +828,19 @@
       <c r="F20">
         <v>1.9990000000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="1">
+        <v>26.174540783028299</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2004</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21">
-        <v>4.0879197100000004</v>
+      <c r="C21" s="1">
+        <v>34.675170899999998</v>
       </c>
       <c r="D21">
         <v>565.45228458621204</v>
@@ -787,16 +851,19 @@
       <c r="F21">
         <v>1.968</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="1">
+        <v>26.802100130797701</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2005</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22">
-        <v>4.3182125100000004</v>
+      <c r="C22" s="1">
+        <v>34.641765589999999</v>
       </c>
       <c r="D22">
         <v>710.74675999486101</v>
@@ -807,16 +874,19 @@
       <c r="F22">
         <v>1.887</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="1">
+        <v>27.428589818770199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2006</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23">
-        <v>4.5697984700000003</v>
+      <c r="C23" s="1">
+        <v>34.697383879999997</v>
       </c>
       <c r="D23">
         <v>807.75664511705395</v>
@@ -827,16 +897,19 @@
       <c r="F23">
         <v>1.873</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="1">
+        <v>28.045829055842201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2007</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24">
-        <v>4.6291761400000002</v>
+      <c r="C24" s="1">
+        <v>34.669078829999997</v>
       </c>
       <c r="D24">
         <v>925.64033834871702</v>
@@ -847,16 +920,19 @@
       <c r="F24">
         <v>1.911</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="1">
+        <v>28.645637050909901</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2008</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25">
-        <v>4.3602833700000003</v>
+      <c r="C25" s="1">
+        <v>34.576129909999999</v>
       </c>
       <c r="D25">
         <v>1163.83195772873</v>
@@ -867,16 +943,19 @@
       <c r="F25">
         <v>1.9330000000000001</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="1">
+        <v>29.219833012869302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2009</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26">
-        <v>4.4850292200000004</v>
+      <c r="C26" s="1">
+        <v>34.635383609999998</v>
       </c>
       <c r="D26">
         <v>1226.1697605153599</v>
@@ -887,16 +966,19 @@
       <c r="F26">
         <v>1.92</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="1">
+        <v>29.758134735567499</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2010</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27">
-        <v>5.0714607200000001</v>
+      <c r="C27" s="1">
+        <v>34.674057009999999</v>
       </c>
       <c r="D27">
         <v>1683.1618244397901</v>
@@ -907,16 +989,19 @@
       <c r="F27">
         <v>1.9059999999999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27" s="1">
+        <v>30.250402725852599</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2011</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28">
-        <v>4.9746851899999998</v>
+      <c r="C28" s="1">
+        <v>34.686904910000003</v>
       </c>
       <c r="D28">
         <v>1950.9250417491301</v>
@@ -927,16 +1012,19 @@
       <c r="F28">
         <v>1.927</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28" s="1">
+        <v>30.699604168099601</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2012</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29">
-        <v>5.0017824199999996</v>
+      <c r="C29" s="1">
+        <v>40.778923030000001</v>
       </c>
       <c r="D29">
         <v>2185.11767654291</v>
@@ -947,16 +1035,19 @@
       <c r="F29">
         <v>1.9670000000000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="1">
+        <v>31.122277940302901</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2013</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
-      <c r="C30">
-        <v>4.41233158</v>
+      <c r="C30" s="1">
+        <v>41.587100980000002</v>
       </c>
       <c r="D30">
         <v>2359.51736472828</v>
@@ -967,16 +1058,19 @@
       <c r="F30">
         <v>1.98</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30" s="1">
+        <v>31.533420172454299</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2014</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
-      <c r="C31">
-        <v>4.6907877899999999</v>
+      <c r="C31" s="1">
+        <v>41.028209689999997</v>
       </c>
       <c r="D31">
         <v>2546.3846445990298</v>
@@ -987,16 +1081,19 @@
       <c r="F31">
         <v>2.09</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31" s="1">
+        <v>31.948026994545401</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2015</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32">
-        <v>4.7114090900000001</v>
+      <c r="C32" s="1">
+        <v>42.13227844</v>
       </c>
       <c r="D32">
         <v>2577.5688534011301</v>
@@ -1007,16 +1104,19 @@
       <c r="F32">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32" s="1">
+        <v>32.3810945365679</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2016</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
-      <c r="C33">
-        <v>4.8699474299999999</v>
+      <c r="C33" s="1">
+        <v>41.356479640000003</v>
       </c>
       <c r="D33">
         <v>2735.0604380415998</v>
@@ -1027,16 +1127,19 @@
       <c r="F33">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" s="1">
+        <v>32.847618928513597</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2017</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
-      <c r="C34">
-        <v>4.9901475900000003</v>
+      <c r="C34" s="1">
+        <v>42.58786774</v>
       </c>
       <c r="D34">
         <v>2956.1099212775298</v>
@@ -1047,16 +1150,19 @@
       <c r="F34">
         <v>1.9850000000000001</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" s="1">
+        <v>33.3625963003742</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2018</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
-      <c r="C35">
-        <v>5.0267882300000002</v>
+      <c r="C35" s="1">
+        <v>44.581008910000001</v>
       </c>
       <c r="D35">
         <v>3222.3100312536599</v>
@@ -1067,16 +1173,19 @@
       <c r="F35">
         <v>1.88</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" s="1">
+        <v>33.941022782141197</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2019</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
-      <c r="C36">
-        <v>4.9740748400000001</v>
+      <c r="C36" s="1">
+        <v>45.117305760000001</v>
       </c>
       <c r="D36">
         <v>3440.9002537543402</v>
@@ -1087,16 +1196,19 @@
       <c r="F36">
         <v>1.9430000000000001</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" s="1">
+        <v>34.623913499951101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2020</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
-      <c r="C37">
-        <v>4.33219814</v>
+      <c r="C37" s="1">
+        <v>42.403350830000001</v>
       </c>
       <c r="D37">
         <v>3534.0395348264701</v>
@@ -1107,16 +1219,19 @@
       <c r="F37">
         <v>1.9570000000000001</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37" s="1">
+        <v>35.570667629974203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2021</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
-      <c r="C38">
-        <v>4.5379242900000003</v>
+      <c r="C38" s="1">
+        <v>40.46375656</v>
       </c>
       <c r="D38">
         <v>3704.1935590038001</v>
@@ -1127,16 +1242,19 @@
       <c r="F38">
         <v>1.9419999999999999</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38" s="1">
+        <v>36.654065642660299</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2022</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
-      <c r="C39">
-        <v>4.5380959499999998</v>
+      <c r="C39" s="1">
+        <v>39.626438139999998</v>
       </c>
       <c r="D39">
         <v>4147.69777213621</v>
@@ -1147,16 +1265,19 @@
       <c r="F39">
         <v>1.927</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" s="1">
+        <v>37.5478515625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2023</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
-      <c r="C40">
-        <v>4.5610947599999996</v>
+      <c r="C40" s="1">
+        <v>39.202846530000002</v>
       </c>
       <c r="D40">
         <v>4323.3503198245098</v>
@@ -1167,6 +1288,12 @@
       <c r="F40">
         <v>1.913</v>
       </c>
+      <c r="G40" s="1">
+        <v>38.129890441894503</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G41" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
